--- a/Project_ETF/ETF_Investment_Portfolio/00919/ETF_Investment_Portfolio_20260603.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00919/ETF_Investment_Portfolio_20260603.xlsx
@@ -1239,17 +1239,17 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>2606</t>
+          <t>2883</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>裕民</t>
+          <t>凱基金</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>38,943,000</t>
+          <t>106,200,000</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -1261,17 +1261,17 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>2883</t>
+          <t>2606</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>凱基金</t>
+          <t>裕民</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>106,200,000</t>
+          <t>38,943,000</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -1393,17 +1393,17 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>4915</t>
+          <t>5871</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>致伸</t>
+          <t>中租-KY</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>26,666,000</t>
+          <t>17,960,000</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -1415,17 +1415,17 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>5871</t>
+          <t>4915</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>中租-KY</t>
+          <t>致伸</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>17,960,000</t>
+          <t>26,666,000</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -1723,17 +1723,17 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>2597</t>
+          <t>9910</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>潤弘</t>
+          <t>豐泰</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>3,700,000</t>
+          <t>8,100,000</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
@@ -1745,17 +1745,17 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>9910</t>
+          <t>9941</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>豐泰</t>
+          <t>裕融</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>8,100,000</t>
+          <t>7,820,000</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
@@ -1767,17 +1767,17 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>9941</t>
+          <t>2597</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>裕融</t>
+          <t>潤弘</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>7,820,000</t>
+          <t>3,700,000</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
@@ -1789,17 +1789,17 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>8422</t>
+          <t>1210</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>可寧衛*</t>
+          <t>大成</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>21,020,000</t>
+          <t>10,780,000</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
@@ -1833,17 +1833,17 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>1210</t>
+          <t>8422</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>大成</t>
+          <t>可寧衛*</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>10,780,000</t>
+          <t>21,020,000</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
